--- a/_work/analysis/02_вопросы_на_решение.xlsx
+++ b/_work/analysis/02_вопросы_на_решение.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Как пользоваться" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Вопросы на решение'!$A$1:$K$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Вопросы на решение'!$A$1:$K$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>ВКО (займ №19 п. 7.4; залог №18 п. 2.3, №17 п. 2.5) — только судебный порядок; остальные — внесудебный и/или судебный. Какой порядок принять?</t>
+          <t>ВКО (займ №19 п. 7.4; залог №18 п. 2.3, №17 п. 2.5) — только судебный порядок в РУССКОМ тексте; в казахском тексте тех же залогов №17 и №18 — «сот және соттан тыс» (судебный и внесудебный), т.е. это также расхождение каз./рус. внутри договора. Остальные регионы — внесудебный и/или судебный. Какой порядок принять?</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2747,10 +2747,2031 @@
       </c>
       <c r="K53" s="2" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Модель сторон на стороне займодателя</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>А1: трехсторонний договор — Займодатель (ГУ) через Поверенного (агента) и Заемщик: №3, №4, №11, №12, №19, №22, №25, №30, №37, №47, №48, №49, №53, №55, №58, №24 (преамбулы); А2: двусторонний — АО-агент выступает «Кредитором» как Поверенный ГУ по договору о госзакупках и договору поручения, ГУ стороной не является; основание — Правила, утв. приказом №272 от 30.06.2023 (№15, преамбула; разд. 12 — реквизиты только Кредитора и Заемщика); А3: четырехсторонний — ГУ «Кредитор», Поверенный (агент), Партнер ТОО «МФО «Ырыс», Заемщик; Партнеру переданы взыскание и обращение взыскания на залог (№61, преамбула, пп. 3.1–3.2, 6.7–6.8); Дополнительно: Созаемщик-физлицо как четвертая сторона (№2, преамбула). В одном тексте нельзя одновременно сделать ГУ стороной договора и исключить его. Одни и те же права (взыскание, мониторинг) закреплены за разными субъектами: Займодатель/Поверенный (№3 пп. 6.3, 6.6), Кредитор-агент (№15 п. 6.3), Партнер (№61 пп. 3.1, 6.8). Вопрос на решение: какие модели сторон допускаются в итоговом договоре — только А1, или А2 и (или) А3 как вариативный блок, или №15 и №61 выделяются в отдельный договор? Допускается ли Созаемщик (№2)?</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 1</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr"/>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Очередность погашения при нормальном платеже</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Сначала основной долг, затем вознаграждение: №22 (п. 2.3); Сначала вознаграждение, затем основной долг: №2 (п. 2.10), №3, №4, №11, №12, №19, №25, №37, №47, №55 (п. 2.3), №30 (п. 2.10), №48, №49 (п. 1.13), №53 (ст. 1 п. 2), №58, №24 (пп. 1.13–1.14). Вопрос на решение: какая очередность применяется?</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 2</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr"/>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Очередность погашения при просрочке или недостаточности платежа</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Первым — основной долг: №3, №4, №11, №12, №19, №22, №37, №47, №55 (п. 2.3), №53 (ст. 1 п. 2), №61 (п. 1.11); Первой — неустойка (штраф, пеня): №2 (п. 2.10), №15 (п. 1.8), №25 (п. 2.3), №30 (п. 2.10), №48, №49 (п. 1.14), №58, №24 (пп. 1.13–1.14). Вопрос на решение: какая очередность применяется при недостаточности платежа?</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 3</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr"/>
+      <c r="I56" s="3" t="inlineStr"/>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Условия досрочного погашения</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Безусловное право без неустойки: №2, №3, №4, №22, №30, №37, №47 (п. 6.1.1), №11, №12, №55 (пп. 6.1.1, 6.5.4), №15, №61 (п. 6.1.4; №61 п. 7.1 подп. 3)), №53 (ст. 4 п. 1 пп. 1)); По согласованию с Заимодателем (№24 — Заимодателем/Поверенным), частичное — не менее 3-кратного ежемесячного платежа: №48, №49, №58, №24 (п. 1.10); Только при отсутствии задолженности по платежам и неустойкам: №25 (п. 6.1.1); Возврат позже 30 календарных дней после выдачи не считается досрочным погашением и расценивается как нецелевое использование: №19 (п. 6.1.1). Вопрос на решение: безусловное ли право досрочного погашения, и допускаются ли ограничения (согласование, минимальная сумма, отсутствие задолженности, правило 30 дней №19)?</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 4</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Порядок обращения взыскания на залог</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Только в судебном порядке: №19 (пп. 6.3.1–6.3.5, 7.4); Во внесудебном и (или) судебном: №2, №11, №22, №25, №30, №55 (п. 7.5), №3, №4 (пп. 6.3.1–6.3.7), №12 (пп. 6.3.3–6.3.5, 8.5), №37 (6.3.3), №47 (п. 6.3.3, разд. 7), №53 (ст. 4 п. 3 пп. 3); ст. 6 п. 4), №58 (п. 2.1.2), №24 (пп. 2.1.2–2.1.3); Во внесудебном: №48, №49 (п. 5.1; п. 2.1.2); Внесудебная реализация по законодательству или Закону об ипотеке: №15 (п. 3.2), №61 (п. 3.2); торги по п. 2 ст. 318 ГК РК: №47 (п. 6.6.8). Вопрос на решение: допускается ли внесудебное обращение взыскания или только судебное?</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 5</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr"/>
+      <c r="I58" s="3" t="inlineStr"/>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Кто выдает письмо о снятии обременения и возвращает оригиналы документов на залог после погашения</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Поверенный: №2, №11, №37, №47 (п. 6.7.2), №3, №4, №55 (пп. 6.7.1–6.7.8; в №3, №4 по тексту «Займодатель обязуется» в разделе Поверенного), №12 (пп. 6.7.1–6.7.3), №19 (пп. 6.7.1–6.7.7), №22, №25 (пп. 6.6.1–6.6.5), №30 (п. 6.7.2 — возврат оригиналов), №53 (оригиналы — ст. 4 п. 6 пп. 8)); Займодатель: №48, №49 (пп. 2.2.1–2.2.2), №58 (пп. 2.2.1–2.2.2), №53 (уведомление для регистрирующего органа — ст. 4 п. 5 пп. 1)). Вопрос на решение: на кого возлагается эта обязанность?</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 6</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Форма расчетов при освоении займа</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Только безналичным путем: №15 (п. 6.2.16), №61 (п. 6.2.17), №55 (п. 6.9.2); безналичное освоение как особое условие — №2 (п. 6.9), №25 (п. 6.2.16); запрет наличных расчетов — №48, №49 (пп. 2.5.12, 1.15.5); Допускается наличная оплата с подтверждением квитанциями к ПКО, распиской, кассовыми чеками: №30 (п. 6.2.1). Вопрос на решение: допускаются ли наличные расчеты за счет займа?</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 7</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr"/>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Страхование заложенного имущества</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Безусловная обязанность страховать до полного исполнения: №3, №4, №11, №12, №22, №47 (п. 6.2.8), №25 (п. 6.2.9), №53 (ст. 4 п. 2 пп. 8)); вместе со страхованием жизни — №2 (п. 6.9.4; в каз. тексте п. 6.2.9), №55 (пп. 6.2.14, 6.9.4 — ежегодно); Только при решении Кредитного комитета: №15 (п. 6.2.12), №61 (п. 6.2.11); Условия нет: №19, №30, №37, №48, №49, №58, №24. Вопрос на решение: страхование залога (и жизни) обязательно, по решению Кредитного комитета или не предусматривается?</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 8</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Условие применения штрафа 25% и досрочного возврата при нецелевом использовании</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>По требованию, без дополнительного условия: №2 (п. 4.2), №3, №4, №11, №12, №19, №22, №25, №37, №47, №55 (п. 4.1), №15 (п. 5.1), №30 (п. 4.2), №53 (ст. 1 п. 3 пп. 3)), №24 (п. 3.3), №61 (разд. 5); «При наличии решения Кредитного комитета»: №58 (пп. 2.5.2, 3.3); «При наличии решения Заимодателя»: №49 (пп. 2.5.2, 3.3), №48 (п. 2.5.2). Безусловное применение санкции и применение только при решении органа нельзя закрепить одновременно. Вопрос на решение: нужно ли для применения санкций за нецелевое использование решение Кредитного комитета или Займодателя?</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 9</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr"/>
+      <c r="I62" s="3" t="inlineStr"/>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Подсудность</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Суд по месту нахождения Займодателя: №2 (пп. 11.1–11.2), №3, №11, №19, №22, №37, №47, №55 (п. 10.2), №4, №12, №30 (п. 11.2), №25 (п. 9.2); По месту нахождения Поверенного: №48, №49 (п. 7.3), №24 (п. 6.3); Займодателя и (или) Поверенного: №53 (ст. 9 п. 2); Специализированный межрайонный экономический суд Атырауской области: №15 (пп. 8.1–8.3); По месту Кредитора, Поверенного, Партнера или их филиалов по выбору: №61 (пп. 9.1–9.4); Не определена (суды РК): №58 (п. 6.3). Вопрос на решение: какая договорная подсудность устанавливается?</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 10</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Арбитраж или государственный суд</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Арбитражная оговорка по ст. 8 Закона РК «Об арбитраже»: №47 (пп. 10.1–10.2, 10.4); Споры — только в судебном порядке: остальные 18 (п. 10 выше; например №2 пп. 11.1–11.2, №15 пп. 8.1–8.3). Вопрос на решение: включается ли арбитражная оговорка?</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 11</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Момент, когда уведомление считается полученным</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>С момента отправки независимо от фактического получения: №47 (п. 11.6); Доставленным при направлении по адресу из договора: №2 (п. 11.3), №3, №19, №22, №47, №55 (п. 10.3), №4, №12, №30 (п. 11.3), №11 (10.3), №25 (п. 9.3), №37 (10.3); Заемщик считается уведомленным — также №48, №49 (п. 7.5), №53 (ст. 9 п. 3), №58, №24 (п. 6.5); На дату вручения, эл. почтой — при отметке о доставке: №15 (п. 6.2.9), №61 (п. 6.2.8). Вопрос на решение: какой момент получения уведомления принимается?</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 12</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Каналы направления претензий о санкциях и уведомлений о расторжении</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Только заказным письмом либо курьером под роспись: №3 (п. 12.1), №4 (п. 13.1), №11 (11.1), №12, №19, №22, №47, №55 (п. 11.1); без «под роспись»: №25 (п. 10.1), №37 (11.1); Допускаются e-mail и WhatsApp: №30 (п. 12.1); WhatsApp: №2 (п. 12.1); Специального порядка нет: №15, №48, №49, №53, №58, №24, №61. Вопрос на решение: допускаются ли электронные каналы и мессенджеры для претензий и уведомлений о расторжении?</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 13</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Приоритет языковых версий</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>При разночтениях приоритетен русский текст: №2 (п. 12.6), №3 (п. 12.5), №4 (п. 13.5), №11 (11.5), №12 (п. 12.5), №15 (п. 11.8), №19, №22, №55 (п. 11.5), №25 (п. 10.5), №30 (п. 12.6), №37 (11.5), №47 (разд. 11), №53 (ст. 10 п. 2), №24 (п. 6.7), №61 (пп. 11.10–11.12); Тексты имеют одинаковую силу, приоритет не установлен: №48, №49 (п. 7.4), №58 (п. 6.4). Вопрос на решение: устанавливается ли приоритет одного из текстов?</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 14</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Передача прав и обязанностей Заемщиком</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Запрет без оговорки о согласии: №30 (п. 10.1), №2 (п. 10.1, рус. текст; в каз. — «без письменного согласия»); Запрет «без письменного согласия» Займодателя или Кредитора (с согласием — допускается): №3 (п. 9.1), №4 (п. 10.1), №11 (9.1), №19, №22, №37, №55 (п. 9.1), №48, №49 (п. 7.7); №12 (разд. 10), №47 (разд. 9); Запрета нет, только правопреемство: №15 (п. 11.6), №53 (ст. 8 п. 1); Условия нет: №25. Вопрос на решение: какой режим передачи прав Заемщиком принимается?</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 15</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Правовая квалификация и наименование предоставляемых средств</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>«Заем»: №37, №48, №49, №58; «Кредит (целевой займ)» / «кредит»: №3, №4, №11, №12, №19, №22, №47, №55; «Микрокредит»: №2, №30, №53, №24; «Бюджетный микрокредит» (приказ №272): №15; «Бюджетный кредит»: №25 (заголовок, пп. 5.2, 6.2.3); №61 (заголовок, пп. 1.1–1.11; Бюджетный кодекс и Закон о микрофинансовой деятельности — п. 6.1.7; в том же тексте «микрокредит» — заголовок разд. 4, п. 1.6 подп. 4), пп. 6.7.6, 6.8.7). От выбора зависят применимые нормы. Например, п. 1.10 №61 об ограничении требований через 180 дней к Заемщику-физлицу при ипотеке жилья. Вопрос на решение: как квалифицируются и называются средства в итоговом договоре (заем / кредит / микрокредит / бюджетный кредит)?</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 1.6, п. 16</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Кто является залогодержателем (модель сторон на стороне кредитора)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>- Залогодержатель — ГУ (Управление), Поверенный (агент) — отдельная сторона и не залогодержатель: №8 (п. 1.1), №9, №10, №17, №18, №21, №27, №38, №45, №50, №52, №54, №59, №24 Прил.3 и Прил.3-1, №61 (преамбулы); в №7 ГУ назван «Займодатель», а в тексте — Залогодержатель (преамбула, п. 1.1). - Два залогодержателя: Залогодержатель 1 — ГУ и «Поверенный (агент)/залогодержатель 2» — АО «СПК «KOKSHE», залог в пользу обоих: №1 (преамбула, пп. 1.1–1.2). - Залогодержатель-1 (ГУ, «Займодатель») и Залогодержатель-2/Поверенный — АО «СПК «Тобол». Ключевые права (переоценка, согласие на распоряжение, выбор способа взыскания, подсудность) принадлежат Залогодержателю-2: №29, №33, №34 (преамбулы; №33 пп. 1.11, 3.2.4, 8.1; №34 пп. 1.6, 3.2.5, 8.1; №29 пп. 2.3 пп. 5, 6.1). - Единственный Залогодержатель — АО-агент, действующее как поверенный ГУ по договору госзакупок услуг и договору поручения; ГУ стороной не является: №16 (преамбула). Вопрос на решение: кто в итоговом договоре является залогодержателем — только ГУ (Поверенный действует от его имени), ГУ и АО «СПК» как два залогодержателя или АО-агент от своего имени?</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 2.6, п. 1</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr"/>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Где хранятся оригиналы правоустанавливающих документов на предмет залога</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>- У Залогодателя: №8 (п. 1.3), №9 (п. 1.3); у Залогодателя, а Залогодержателю передаётся нотариальная копия: №33 (п. 1.8). - У Залогодержателя: №10 (пп. 1.3, 2.3.6), №16 (пп. 1.2, 2.3 пп. 8), №45 (пп. 1.3, 2.2.1), №61 (пп. 1.2, 2.3 пп. 8), №7 (п. 1.6), №29 (п. 2.4 пп. 1); у Залогодержателя 1: №1 (пп. 1.3, 2.2.2); у Залогодержателя-2: №34 (пп. 1.3, 2.2.2); у Залогодержателя и/или Поверенного: №17, №18 (п. 1.3). - У Поверенного (агента): №21 (п. 1.3), №38 (п. 1.4), №50 (п. 1.4), №52 (п. 1.3), №54 (п. 1.3), №59 (п. 1.4); передаются Поверенному, а хранятся у Залогодержателя: №24 Прил.3 и Прил.3-1 (п. 1.4). Вопрос на решение: у кого хранятся оригиналы документов на предмет залога в течение срока договора?</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 2.6, п. 2</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr"/>
+      <c r="I71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Кто оплачивает независимого оценщика при переоценке в момент обращения взыскания</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>- Поверенный (агент), с удержанием из выручки: №8, №9, №17, №18, №21, №27, №45, №54 (п. 1.5), №38, №52 (п. 1.6). - Залогодержатель, с удержанием из выручки: №10 (п. 1.5). - Залогодатель: №29 (п. 1.10), №33 (п. 1.11, с удержанием из выручки), №34 (п. 1.6, с удержанием), №50 (п. 1.6), №59 (п. 1.6); в №1 (п. 1.6) — сторона-инициатор с удержанием из выручки, а в каз. тексте — Залогодатель. - Расходы Залогодержателя, которые включаются в сумму взыскания с Заемщика/Залогодателя: №24 Прил.3 и Прил.3-1 (п. 1.6). Вопрос на решение: на кого возлагается оплата оценки при обращении взыскания и удерживается ли она из выручки?</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 2.6, п. 3</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr"/>
+      <c r="I72" s="3" t="inlineStr"/>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Страхование предмета залога</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>- «Предмет залога не подлежит страхованию»: №29 (п. 1.12). - Обязательное страхование: №1 (п. 2.2.14), №33 (п. 2.2.2), №52 (п. 2.2.13), №54 (п. 2.2.13); по решению Кредитного комитета: №16 (п. 2.3 пп. 10). - Условия о страховании нет: №7, №8, №9, №10, №17, №18, №21, №24 обе, №27, №34, №38, №45, №50, №59, №61. Вопрос на решение: обязательно ли страхование предмета залога и распространяется ли запрет страхования из №29 (п. 1.12) на какие-либо виды имущества?</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 2.6, п. 4</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr"/>
+      <c r="I73" s="3" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Способ реализации предмета залога: только судебный или также внесудебный</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>- Только судебный: №17 (рус. п. 1.1, 3-й абз.; п. 2.3; п. 2.5 — Поверенный проводит мероприятия «по судебной реализации»), №18 (рус. пп. 1.1, 2.3, 2.5). - Судебный или внесудебный: №8 (пп. 2.3.1, 3.4), №9 (пп. 1.1, 2.3.1, 2.5.6), №10 (п. 2.3.1), №16 (пп. 2.1, 3.1), №21 (пп. 1.2, 2.3), №27 (пп. 1.1, 2.3.1), №38 (пп. 1.1, 2.5.6), №45 (п. 1.1, 2.5), №50 (п. 1.2), №52 (пп. 1.1, 2.3), №54 (пп. 1.1, 2.3.1), №59 (пп. 1.2, 2.5), №24 Прил.3 (пп. 1.2, 2.5) и Прил.3-1 (пп. 1.2, 2.3.1, 2.5.6), №61 (п. 3.1); на усмотрение залогодержателя — судебный или принудительный внесудебный: №1 (п. 6.7), №29 (п. 4.7), №33, №34 (п. 6.7); внесудебный допускается: №7 (п. 2.1.2). - Дефект, мешающий унификации: в каз. тексте №17 и №18 допускается «сот және соттан тыс» (судебная и внесудебная) реализация (№17 каз. п. 1.1 абз. 2, пп. 2.3.1, 2.5.6; №18 каз. п. 1.1 абз. 2, пп. 2.3.1, 2.5.6). Судебный порядок только в рус. тексте. Вопрос на решение: допускается ли в итоговом договоре внесудебная реализация предмета залога или только судебная?</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 2.6, п. 5</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr"/>
+      <c r="I74" s="3" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Может ли Залогодатель реализовать предмет без согласия залогодержателя</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>- Может: реализованное Залогодателем имущество перестаёт быть предметом залога с перехода права собственности к приобретателю, а приобретаемое становится предметом залога; запрета и требования согласия нет: №7 (Приложение №1; п. 2.3.1). - Запрет отчуждения без предварительного письменного согласия: остальные 21 договор (№1 п. 2.2.5; №8, №9, №10 п. 2.2.8; №16, №61 п. 2.3 пп. 4; №33 п. 2.2.6 и др., см. 2.3, п. 7). Вопрос на решение: допускается ли для движимого имущества (оборотного) свободная реализация Залогодателем с заменой предмета, как в №7, или действует общий запрет отчуждения без согласия?</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 2.6, п. 6</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Кому платятся штрафы 10% (нарушение п. 2.2) и 5% (недостоверные заверения)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>- Поверенному (агенту): №8 (пп. 5.4–5.5), №9, №10, №17, №18, №21, №27, №38, №45, №52, №54; в №8 и №27 прямо «а не Залогодержателю». - Залогодержателю: №59 (разд. 5, 4–5-й абз.). - Получатель не указан: №50 (разд. 5), №24 Прил.3 (разд. 5), №24 Прил.3-1 (пп. 5.4–5.5). Вопрос на решение: в чью пользу взыскиваются штрафы 10% и 5% по договору залога?</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 2.6, п. 7</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr"/>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Одностороннее изменение договора залогодержателем</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>- Допускается уведомлением, без допсоглашения: №7 (п. 2.1.5, при изменении вида залога), №16 (п. 8.5), №61 (п. 6.5; при изменении ставки, ГЭСВ, графика, сроков по кредитному договору). - Изменения только письменным допсоглашением, подписанным Сторонами: №8, №9, №10, №18, №21, №38, №50, №52, №54 (п. 6.4), №17, №27, №45, №59, №24 Прил.3 (разд. 6), №24 Прил.3-1 (п. 6.4), №1, №33, №34 (п. 9.2), №29 (п. 7.2). Вопрос на решение: вправе ли залогодержатель изменять договор залога в одностороннем порядке уведомлением, и если да, в каких случаях?</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 2.6, п. 8</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Подсудность споров</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>- По месту нахождения Залогодержателя 1 и Залогодержателя 2: №1 (п. 8.2); по месту нахождения Залогодержателя: №7 (п. 3.5); Залогодержателя-2: №29 (пп. 6.1–6.2), №33, №34 (пп. 8.1–8.2); Поверенного (агента): №50 (п. 6.3). - Специализированный межрайонный экономический суд Атырауской области: №16 (п. 5.2). - По месту нахождения Залогодержателя/Поверенного/Партнера или их филиалов, на их усмотрение: №61 (рус. п. 5.2; в каз. п. 5.2 — только по месту нахождения кредитора). - Подсудность не установлена: №8, №9, №10, №18, №21, №38, №54, №24 Прил.3-1 (п. 6.3), №17, №27, №45, №52, №59, №24 Прил.3 (разд. 6). Вопрос на решение: устанавливается ли договорная подсудность и по месту нахождения какой стороны (включая Партнера)?</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 2.6, п. 9</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr"/>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Приоритет текста на государственном и русском языках</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>- Тексты равной силы, приоритета нет: №1, №33, №34 (п. 9.6). - При разночтении приоритет у русского текста: №7 (п. 3.7), №8, №9, №10, №17, №18, №21, №27, №38, №45, №50, №52, №54, №59, №24 обе (п. 6.5 / разд. 6), №16 (п. 8.11), №61 (п. 6.11), №29 (п. 7.6). - Примечание: в одном регионе (Костанай) обе редакции — №29 (п. 7.6) с приоритетом русского текста, №33 и №34 (п. 9.6) без приоритета. Вопрос на решение: какой текст имеет приоритет при расхождении — русский или оба равной силы?</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 2.6, п. 10</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr"/>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Одностороннее расторжение договора</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>- Право одностороннего (внесудебного) расторжения при нарушении антикоррупционной оговорки: №1, №33, №34 (п. 7.4), №16 (п. 7.6), №29 (п. 5.4). - Одностороннее расторжение не допускается, кроме случаев по законодательству: №24 Прил.3 (разд. 4), №8, №9, №21, №52, №54, №24 Прил.3-1 (п. 4.3), №27, №45, №50, №59 (разд. 4); не допускается без оговорки: №1, №33, №34 (п. 9.3), №29 (п. 7.3) (внутри одного договора у №1, №29, №33, №34 оба условия сосуществуют как общее правило и исключение). - В №50 (пп. 7.1–7.4) право расторжения по антикоррупционной оговорке относится к Договору займа, а не к договору залога. Вопрос на решение: включать ли право одностороннего расторжения договора залога (по антикоррупционной оговорке) или сохранить общий запрет одностороннего расторжения?</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 2.6, п. 11</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Момент вступления договора в силу</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>- С государственной регистрации: №1 (п. 9.1), №29 (п. 7.1), №33, №34 (п. 9.1). - С подписания: №7 (п. 3.1), №8, №9, №10, №18, №21, №38, №24 Прил.3-1 (п. 4.1), №17, №27, №45, №50, №24 Прил.3 (разд. 4), №16 (п. 8.1), №61 (п. 6.1). Вопрос на решение: вступает ли договор залога в силу с подписания или с государственной регистрации?</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 2.6, п. 12</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr"/>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Момент возникновения права залога</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>- С подписания договора: №7 (п. 3.1). - С государственной регистрации: остальные договоры, где условие есть (№1 п. 1.4; №8, №9 п. 4.2; №21 п. 4.2; №27 разд. 4; №33 п. 1.9; №50, №24 обе п. 4.2 / п. 1.5; №16 Термины; №61 пп. 6.1, 6.8 и др., см. 2.3, п. 8). Вопрос на решение: сохраняется ли для движимого имущества возникновение права залога с подписания (№7) или для всех видов — с государственной регистрации?</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 2.6, п. 13</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr"/>
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Гарантия</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Документы о неисполнении Заемщиком при предъявлении требования к Гаранту</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Вариант А — документы не требуются, договор является подтверждающим документом для безакцептного изъятия/списания: №5, №6, №13, №14, №20, №26, №46, №61 (п. 2.3); №28, №57, №24 (п. 2.8). Вариант Б — Займодатель и/или Поверенный (агент) обязан предоставить Гаранту документы, подтверждающие неисполнение Заемщиком: №51 Жетісу (п. 2.4). Вопрос: требуется ли для предъявления требования к Гаранту представление документов о неисполнении Заемщиком, или договор сам служит основанием для безакцептного списания без таких документов? (объединяет вопросы №36 и №37 этапа 2)</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 3.6, п. 1</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr"/>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Гарантия</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Условие прекращения обязательства Гаранта / договора</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Вариант А — «Гарантия прекращается при полном исполнении Заемщиком или Гарантом всех своих обязательств»: №5, №6, №13, №20, №26, №46 (п. 1.5); в этих же договорах п. 3.2 изложен смешанно («Заемщика/Гаранта … и Гарантом по настоящему Договору»). Вариант Б — «Действие настоящего Договора прекращается с момента полного исполнения обязательств Заемщика … и Гарантом по настоящему Договору»: №28, №51, №57, №24 (п. 3.1), №14, №61 (п. 3.3); при этом в №14 и №61 п. 1.5 — только «при полном исполнении Заемщиком». Вопрос: прекращается ли обязательство Гаранта при полном исполнении основного обязательства любым из них или только после полного исполнения и Заемщиком, и Гарантом своих обязательств (включая обязательства по самому договору гарантии)? (вопрос №38 этапа 2)</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 3.6, п. 2</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="3" t="inlineStr"/>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Гарантия</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Уступка кредиторской стороной прав по договору гарантии</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Вариант А — без письменного согласия Гаранта вправе переуступать права любому третьему лицу: №28 Костанай (п. 2.12, Бенефициар), №57 СКО (п. 2.12, Бенефициар/Поверенный (агент)), №24 ЗКО Прил.4 (п. 2.12, Заимодатель/Поверенный (агент)). Вариант Б — Займодатель и/или Поверенный (агент) без письменного согласия Гаранта не вправе переуступать права и обязанности третьим лицам: №51 Жетісу (п. 2.11). В №5, №6, №13, №14, №20, №26, №46, №61 условие отсутствует. Вопрос: допускается ли уступка прав по договору гарантии без согласия Гаранта, только с его письменного согласия, либо условие не включается? (вопрос №39 этапа 2, вариант А дополнен №24)</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 3.6, п. 3</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr"/>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Поручение</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Односторонний отказ / расторжение договора поручения по инициативе одной стороны</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>№35 Кызылорда: «Односторонний отказ от исполнения Договора не допускается» (п. 9.2), иных оснований расторжения нет. №43 Мангистау: Стороны вправе расторгнуть Договор по инициативе любой из Сторон либо по обоюдному волеизъявлению путем подписания Соглашения о расторжении и полного взаиморасчета (разд. «Основные функции, права и обязанности сторон», абз. «Стороны вправе расторгнуть Договор»); при невозможности устранить отсутствие разрешений госорганов агент инициирует расторжение (п. 6.2); срок уведомления не указан. Вопрос на решение: допускается ли в итоговом договоре поручения расторжение по инициативе одной стороны (как в №43) или односторонний отказ запрещается (как в №35)?</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 4.6, п. 1</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr"/>
+      <c r="I86" s="3" t="inlineStr"/>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>ДКП (лизинг)</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Состав подписантов Акта приёма-передачи</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Двусторонний Акт (Продавец и Лизингополучатель): №31 Костанай, пп. 7.1, 7.2. Трёхсторонний Акт с участием Покупателя/Лизингодателя: №23 ЗКО, Прил. 2; №63 Туркестан, п. 7.1 (Покупатель в лице Партнёра ТОО «МФО «Ырыс»). Вопрос: подписывает ли Акт Покупатель (лизингодатель) или только Продавец и Лизингополучатель?</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 5.6, п. 1</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr"/>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>ДКП (лизинг)</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Носитель риска случайной гибели Товара до подписания Акта</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Лизингодатель (Покупатель): №23 ЗКО, Прил. 2, 3-й маркер. Продавец: №31 Костанай, п. 7.5; №63 Туркестан, п. 7.3. Вопрос: на ком лежит риск до подписания Акта — на Продавце или на Покупателе (лизингодателе)?</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 5.6, п. 2</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr"/>
+      <c r="I88" s="3" t="inlineStr"/>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>ДКП (лизинг)</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Самостоятельность ДКП или неотъемлемость от Договора финансового лизинга</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Самостоятельный ДКП, отношения по лизингу — в отдельном Договоре финансового лизинга: №31 Костанай, пп. 13.3, 13.5, 2.4. Неотъемлемая часть Договора финансового лизинга и лизинговой сделки, с обязанностями и ответственностью Лизингополучателя в ДКП: №63 Туркестан, пп. 1.2, 10.8, 13.5, 9.1–9.11, 10.7, 10.8.1. №23 ЗКО — прямого условия нет (Прил. 2: Акт — часть обоих договоров). Вопрос: ДКП самостоятельный или неотъемлемая часть Договора финансового лизинга, и включать ли в ДКП обязанности Лизингополучателя по лизинговой сделке?</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 5.6, п. 3</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Финансовый лизинг</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Состав стороны «Лизингодатель»</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Вариант 1: одно юрлицо — АО «СПК» (№32, преамбула; №24, преамбула). Вариант 2: АО «СПК «Туркестан» как «Поверенный (агент)»/«Лизингодатель» и ТОО «МФО «Ырыс» («Партнер») совместно образуют одну сторону, права и обязанности относятся к обоим в равной степени; передача предмета — «от Лизингодателя в лице Партнера» (№65, преамбула; п. 1.1, 2.1; разд. 12). Вопрос на решение: допускается ли в итоговом договоре модель «агент + партнёр-МФО как одна сторона» (вариант блока А) или лизингодателем может быть только одно лицо?</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 6.6, п. 1</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr"/>
+      <c r="I90" s="3" t="inlineStr"/>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Финансовый лизинг</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Правовая квалификация договора</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Вариант 1: договор финансового лизинга без элементов кредита; в №24 — «чистый финансовый лизинг» (№32, разд. 1; №24, п. 1.5). Вариант 2: лизингодатель и партнёр «предоставляют бюджетный кредит» в соответствии с договором лизинга, указывается ГЭСВ бюджетного кредита 2,7%, «микрокредит», «микрофинансовая организация» (№65, п. 1.1, 1.4, 3.4, 3.11.6). Вопрос на решение: квалифицировать ли итоговый договор только как финансовый лизинг или сохранять в нём формулировки о бюджетном кредите/микрокредите и ГЭСВ?</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 6.6, п. 2</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr"/>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Финансовый лизинг</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Форма первоначального взноса</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Вариант 1: только денежный взнос 20%, в течение 5 рабочих дней, до оплаты продавцу; неуплата — существенное нарушение и право внесудебного отказа (№24, п. 1.23–1.24). Вариант 2: денежный 20% либо имущество в счёт взноса с отражением полной суммы предмета в Графике (№32, п. 4.10, 4.12). Вариант 3: взноса нет, вместо него — залог недвижимости лизингополучателя; передача предмета — при исполнении этого условия (№65, п. 3.2.1, 2.6). Внутренние дефекты: №32 п. 2.2 (участие 20%) против п. 2.5 (финансирование 100%); №65 п. 7.2 подп. 4), 7.8, 7.9 называют залог по п. 3.2.1 «внесёнными первоначальными взносами», не подлежащими возврату. Вопрос на решение: какие формы исполнения обязанности по первоначальному взносу допускаются (деньги / имущество / залог вместо взноса) и является ли денежный взнос обязательным условием передачи предмета?</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 6.6, п. 3</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr"/>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Финансовый лизинг</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Очерёдность погашения при недостаточности платежа</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Вариант 1: расходы по взысканию → неустойка → просроченное вознаграждение → просроченный основной долг → текущее вознаграждение → текущий основной долг (№32, п. 4.7). Вариант 2: основной долг → вознаграждение → неустойка → основной долг текущего периода → вознаграждение текущего периода → издержки МФО; лизингодатель вправе в одностороннем порядке изменить очерёдность (№65, п. 3.11, 3.12). Вариант 3: издержки лизингодателя → неустойки → вознаграждение → Общая стоимость; лизингодатель вправе принять платёж в иной очерёдности и направить на иные договоры (№24, п. 1.15–1.16). Вопрос на решение: какую очерёдность погашения закрепить и допускается ли её одностороннее изменение лизингодателем?</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 6.6, п. 4</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr"/>
+      <c r="I93" s="3" t="inlineStr"/>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Финансовый лизинг</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Перенос срока платежа, выпавшего на нерабочий день</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Вариант 1: на предшествующий рабочий день (№65, п. 3.5). Вариант 2: на следующий рабочий день (№24, п. 1.13). №32 — не урегулировано. Вопрос на решение: в какую сторону переносится срок платежа?</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 6.6, п. 5</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr"/>
+      <c r="I94" s="3" t="inlineStr"/>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Финансовый лизинг</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Минимальный срок до перехода права собственности и до прекращения договора</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Вариант 1: переход права при полном исполнении, в т.ч. досрочном, без минимального срока; договор действует до полного исполнения (№32, п. 5.1.5, 7.2, 10.6, 3.6, 14.7; №65, п. 1.5, 4.4.3, 11.1). Вариант 2: переход — по истечении срока или досрочно, но не ранее 3 лет с оформления Приложения №3; договор действует не ранее 3 лет, пп. 6.2.27 и 6.2.33 — 5 лет (№24, разд. 7, разд. 11, п. 6.5). Дефект: в каз. тексте №24 разд. 11 — «3 (үш) күннен», «5 (бес) күн» (дней). Вопрос на решение: устанавливается ли минимальный 3‑летний срок до перехода права собственности и прекращения договора (и 5‑летний срок для отдельных обязательств)?</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 6.6, п. 6</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr"/>
+      <c r="I95" s="3" t="inlineStr"/>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Финансовый лизинг</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Досрочное погашение</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Вариант 1: полное или частичное — в любое время при предварительном письменном уведомлении, без ограничения размера (№32, п. 10.1–10.5). Вариант 2: частичное — в любое время, платежи за первые 12 месяцев не более 50% окончательной стоимости, уведомление за 10 календарных дней; полное — и до 37 месяцев, с возмещением налоговых потерь (№65, п. 3.9.1–3.9.3). Вариант 3: по согласованию с лизингодателем; частичное — не более 50% Общей стоимости за первый год; полное — только по истечении 3 лет с даты заключения; уведомление за 1 рабочий день (№24, п. 6.1.4–6.1.5, 6.2). Вопрос на решение: допускается ли полное досрочное погашение до истечения 3 лет, требуется ли согласие лизингодателя и ограничивается ли объём частичного погашения?</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 6.6, п. 7</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr"/>
+      <c r="I96" s="3" t="inlineStr"/>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Финансовый лизинг</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Исключения из обязанности страхования</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Вариант 1: страхование на весь срок без исключений (№32, п. 8.2; №65, п. 4.2.4 подп. 5), 6.1.1–6.1.3). Вариант 2: страхование не требуется, если остаток неоплаченной стоимости на дату заключения не превышает 10% Общей стоимости (№24, п. 6.2.25). Дефект №24: срок страхования 30 рабочих дней (п. 6.2.25) против 15 календарных дней на оригиналы и премию (разд. 9, 4-й абзац; пункты не пронумерованы). Вопрос на решение: сохраняется ли исключение из обязанности страхования при остатке ≤10%?</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 6.6, п. 8</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr"/>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Финансовый лизинг</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Подсудность</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Вариант 1: Специализированный межрайонный экономический суд Южно-Казахстанской области (№65, п. 10.1–10.2). Вариант 2: суд по месту нахождения лизингодателя (№24, разд. 13). Вариант 3: суд по законодательству РК без указания конкретного суда (№32, п. 14.5–14.6). Вопрос на решение: какую договорную подсудность указать в итоговом договоре (конкретный суд, место нахождения лизингодателя или общие правила)?</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 6.6, п. 9</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr"/>
+      <c r="I98" s="3" t="inlineStr"/>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Финансовый лизинг</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Юридическая сила казахского и русского текстов</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Вариант 1: тексты имеют равную юридическую силу (№32, п. 14.8; №65, п. 11.9 со ссылкой на ст. 15 Закона «О языках»). Вариант 2: язык сделки — русский, при разночтениях приоритет русского текста (№24, разд. 13). Вопрос на решение: устанавливать ли приоритет одного из текстов?</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 6.6, п. 10</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr"/>
+      <c r="I99" s="3" t="inlineStr"/>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Поручение</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Правовая модель передачи средств агенту</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Модель А — заем Доверителя агенту под 1% годовых на 10 лет с возвратом агентом по графику (№35 Кызылорда, разд. 1, пп. 2.3, 2.4, 2.10; Приложение №1). Модель Б — средства для обслуживания бюджетного кредита, агент перечисляет в бюджет поступившее от Заемщиков и не отвечает за их неисполнение (№43 Мангистау, пп. 1.1, 1.5, 5.1.4). На этапе 2 не признано противоречием, но в одном договоре обе модели одновременно не применить. Какую модель принять?</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, разделы 4.2 и 4.4</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr"/>
+      <c r="I100" s="3" t="inlineStr"/>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K53"/>
+  <autoFilter ref="A1:K100"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Открыт,В работе,Решён,Отложен"</formula1>
     </dataValidation>
   </dataValidations>

--- a/_work/analysis/02_вопросы_на_решение.xlsx
+++ b/_work/analysis/02_вопросы_на_решение.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Как пользоваться" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Вопросы на решение'!$A$1:$K$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Вопросы на решение'!$A$1:$K$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4768,10 +4768,53 @@
       </c>
       <c r="K100" s="2" t="inlineStr"/>
     </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>ДКП (лизинг)</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Четвёртая сторона «Партнёр» (ТОО «МФО «Ырыс») в ДКП</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>№23 ЗКО и №31 Костанай — три стороны (Продавец, Покупатель, Лизингополучатель; преамбулы). №63 Туркестан — отдельной стороной указан «Партнёр» ТОО «МФО «Ырыс» по доверенности и договору о совместной деятельности (преамбула); через него Покупатель — грузополучатель (п. 4.1) и участник приёмки и Акта (п. 7.1); при этом п. 13.3 — три экземпляра. Включать ли Партнёра в итоговый ДКП как необязательный блок Б или оставить региональной особенностью вне единого шаблона?</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>03_унификация.md, раздел 5.7, п. 1; 04_структура_дкп.md, блок Б</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Юрист, руководитель</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr"/>
+      <c r="I101" s="3" t="inlineStr"/>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K100"/>
+  <autoFilter ref="A1:K101"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Открыт,В работе,Решён,Отложен"</formula1>
     </dataValidation>
   </dataValidations>

--- a/_work/analysis/02_вопросы_на_решение.xlsx
+++ b/_work/analysis/02_вопросы_на_решение.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Вопросы на решение" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Как пользоваться" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вопросы на решение" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как пользоваться" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Вопросы на решение'!$A$1:$K$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Вопросы на решение'!$A$1:$K$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4811,10 +4811,53 @@
       </c>
       <c r="K101" s="2" t="inlineStr"/>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Этап 3</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Займ</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Право Поверенного в одностороннем порядке изменять условия договора</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>№48, №49 (п. 2.3.5; уведомление — п. 2.4.4): Поверенный вправе «в одностороннем порядке изменять условия настоящего Договора при изменении законодательства Республики Казахстан, а также в связи с изменениями, основанными на решениях Президента, Правительства Республики Казахстан». При этом №49 п. 7.2 — «Условия настоящего Договора могут быть изменены только по взаимному согласию Сторон» без исключений; в других договорах — «за исключением случаев, предусмотренных настоящим Договором» (№3 п. 12.3 и др.). Противоречат ли эти положения друг другу и включать ли право одностороннего изменения в единый договор?</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>черновик_договор_займа.docx, пп. 6.6.12, 6.7.10</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Юрист</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr"/>
+      <c r="I102" s="3" t="inlineStr"/>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K101"/>
+  <autoFilter ref="A1:K102"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Открыт,В работе,Решён,Отложен"</formula1>
     </dataValidation>
   </dataValidations>
